--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97489</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Mathias Molau</t>
+          <t>Mathias Molau, Sandra Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mathias Molau, Sandra Johansson</t>
+          <t>Sandra Johansson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97497</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mathias Molau, Sandra Johansson</t>
+          <t>Sandra Johansson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97619</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129949370</v>
       </c>
       <c r="B2" t="n">
-        <v>97619</v>
+        <v>97811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,217 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129949533</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97785</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>359801</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6393131</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Mathias Molau</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126294684</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ösjöns utlopp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>359790</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6393141</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per-Anders Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per-Anders Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30655-2023 artfynd.xlsx
+++ b/artfynd/A 30655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949370</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,8 +995,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126294684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>